--- a/data/trans_orig/IP2002-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2002-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21143</t>
+          <t>21050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82165</t>
+          <t>82225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91507</t>
+          <t>91650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79877</t>
+          <t>80179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88179</t>
+          <t>88152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166227</t>
+          <t>166320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178273</t>
+          <t>177906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70976</t>
+          <t>72154</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79406</t>
+          <t>79343</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75126</t>
+          <t>76128</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81874</t>
+          <t>81896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150014</t>
+          <t>151466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>160006</t>
+          <t>160477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56494</t>
+          <t>55312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>62745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87522</t>
+          <t>87469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95121</t>
+          <t>95163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146894</t>
+          <t>147000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157004</t>
+          <t>156910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175559</t>
+          <t>175446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185431</t>
+          <t>185445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171284</t>
+          <t>170036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>181511</t>
+          <t>181763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349958</t>
+          <t>349790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364563</t>
+          <t>365150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28020</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87478</t>
+          <t>87210</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96262</t>
+          <t>96150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102293</t>
+          <t>102057</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113254</t>
+          <t>113415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193772</t>
+          <t>193004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207271</t>
+          <t>207409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62803</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69592</t>
+          <t>69487</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57107</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63768</t>
+          <t>63772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122632</t>
+          <t>121743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>131992</t>
+          <t>132154</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>30499</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50925</t>
+          <t>50358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34575</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56981</t>
+          <t>56369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70363</t>
+          <t>71196</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99222</t>
+          <t>101792</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>555082</t>
+          <t>555649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>574986</t>
+          <t>575508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>591393</t>
+          <t>592005</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>613799</t>
+          <t>613201</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1155159</t>
+          <t>1152589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1184018</t>
+          <t>1183185</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78243</t>
+          <t>78538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83314</t>
+          <t>83300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75119</t>
+          <t>75069</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80820</t>
+          <t>81371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155641</t>
+          <t>156036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163385</t>
+          <t>163489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>80384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86026</t>
+          <t>86046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84684</t>
+          <t>84450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90814</t>
+          <t>90710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167448</t>
+          <t>167353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176020</t>
+          <t>175553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>75160</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80597</t>
+          <t>80590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74121</t>
+          <t>74416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80286</t>
+          <t>80284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152662</t>
+          <t>152642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>160208</t>
+          <t>160195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171185</t>
+          <t>171710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182530</t>
+          <t>183174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190083</t>
+          <t>190068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201944</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366950</t>
+          <t>365696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>383125</t>
+          <t>382443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20708</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38402</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117310</t>
+          <t>117403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129229</t>
+          <t>128546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108952</t>
+          <t>109068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121599</t>
+          <t>122036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>231042</t>
+          <t>230986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>248736</t>
+          <t>247927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45157</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58615</t>
+          <t>57749</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66325</t>
+          <t>66636</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105993</t>
+          <t>106455</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115120</t>
+          <t>115302</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25959</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>44502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56927</t>
+          <t>56054</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>65488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94385</t>
+          <t>93359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584578</t>
+          <t>585542</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>604085</t>
+          <t>604007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>610174</t>
+          <t>611047</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>633030</t>
+          <t>632498</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1202760</t>
+          <t>1203786</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1231157</t>
+          <t>1231657</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68168</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75484</t>
+          <t>75571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83827</t>
+          <t>82969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89438</t>
+          <t>89446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155096</t>
+          <t>154438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164124</t>
+          <t>163652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90705</t>
+          <t>91087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96466</t>
+          <t>96450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97863</t>
+          <t>97642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104214</t>
+          <t>104203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191443</t>
+          <t>191052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199437</t>
+          <t>199755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50279</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>57098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61571</t>
+          <t>61394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68803</t>
+          <t>68752</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114750</t>
+          <t>115347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124397</t>
+          <t>124474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>20629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>17846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>34486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189810</t>
+          <t>189695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200648</t>
+          <t>200242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182128</t>
+          <t>182506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194543</t>
+          <t>194549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376426</t>
+          <t>376414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>392201</t>
+          <t>393054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18055</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>24787</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112847</t>
+          <t>111887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124281</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124641</t>
+          <t>124164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133212</t>
+          <t>132873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241365</t>
+          <t>241200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>254723</t>
+          <t>254838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47710</t>
+          <t>47719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55036</t>
+          <t>54751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59073</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109728</t>
+          <t>109265</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118163</t>
+          <t>118305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28710</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50638</t>
+          <t>50816</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>24119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43470</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59143</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87225</t>
+          <t>85703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577619</t>
+          <t>577441</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599547</t>
+          <t>598004</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626246</t>
+          <t>626964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>644938</t>
+          <t>645597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1210748</t>
+          <t>1212270</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1238830</t>
+          <t>1240470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26163</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88844</t>
+          <t>88856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120848</t>
+          <t>120441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131750</t>
+          <t>131445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>213214</t>
+          <t>212887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227403</t>
+          <t>227950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83923</t>
+          <t>84575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92359</t>
+          <t>92609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85217</t>
+          <t>84148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92111</t>
+          <t>91989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172371</t>
+          <t>172847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183426</t>
+          <t>183213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41504</t>
+          <t>41350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48439</t>
+          <t>48493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>55459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62359</t>
+          <t>62360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101521</t>
+          <t>100940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110178</t>
+          <t>109958</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>16946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30517</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195083</t>
+          <t>194990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207142</t>
+          <t>207644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196683</t>
+          <t>195660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207394</t>
+          <t>206962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396055</t>
+          <t>395940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412369</t>
+          <t>412264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105248</t>
+          <t>105144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114533</t>
+          <t>114874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148086</t>
+          <t>147987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158021</t>
+          <t>158153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257902</t>
+          <t>257669</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271100</t>
+          <t>270946</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59273</t>
+          <t>58252</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60925</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69517</t>
+          <t>69554</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124735</t>
+          <t>125385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136881</t>
+          <t>137082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>49840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23734</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45517</t>
+          <t>46399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57923</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88094</t>
+          <t>88555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>597661</t>
+          <t>598228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>619382</t>
+          <t>619763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>689583</t>
+          <t>688701</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711366</t>
+          <t>710938</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1295074</t>
+          <t>1294613</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1325245</t>
+          <t>1325803</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
